--- a/printer-history.xlsx
+++ b/printer-history.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История" sheetId="1" r:id="Re8bf280b3eee41ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="2" r:id="Rbd83c1982ed345be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="История" sheetId="1" r:id="Rf1431eea1e774955"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="2" r:id="Re8318e50b24641a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -371,25 +371,8 @@
     <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="12" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="20" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="22" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="28" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="45" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="55" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -406,61 +389,10 @@
         <x:v>Название</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Описание устройства</x:v>
+        <x:v>Всего напечатано</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
-        <x:v>Расположение</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="str">
-        <x:v>Инвентарный номер</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="str">
-        <x:v>Серийный номер</x:v>
-      </x:c>
-      <x:c r="I1" s="6" t="str">
-        <x:v>Принтер определён</x:v>
-      </x:c>
-      <x:c r="J1" s="6" t="str">
-        <x:v>Источник</x:v>
-      </x:c>
-      <x:c r="K1" s="6" t="str">
-        <x:v>SNMP</x:v>
-      </x:c>
-      <x:c r="L1" s="6" t="str">
-        <x:v>Всего напечатано</x:v>
-      </x:c>
-      <x:c r="M1" s="6" t="str">
-        <x:v>Печать</x:v>
-      </x:c>
-      <x:c r="N1" s="6" t="str">
-        <x:v>Копирование</x:v>
-      </x:c>
-      <x:c r="O1" s="6" t="str">
-        <x:v>Факс</x:v>
-      </x:c>
-      <x:c r="P1" s="6" t="str">
         <x:v>Всего отсканировано</x:v>
-      </x:c>
-      <x:c r="Q1" s="6" t="str">
-        <x:v>Сканирование: копии</x:v>
-      </x:c>
-      <x:c r="R1" s="6" t="str">
-        <x:v>Сканирование: другое</x:v>
-      </x:c>
-      <x:c r="S1" s="6" t="str">
-        <x:v>Длина печати, км</x:v>
-      </x:c>
-      <x:c r="T1" s="6" t="str">
-        <x:v>Остаток, %</x:v>
-      </x:c>
-      <x:c r="U1" s="6" t="str">
-        <x:v>Метод определения</x:v>
-      </x:c>
-      <x:c r="V1" s="6" t="str">
-        <x:v>HTTP-страница</x:v>
-      </x:c>
-      <x:c r="W1" s="6" t="str">
-        <x:v>Ошибка / предупреждения</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -519,7 +451,7 @@
         <x:v>Фильтрация</x:v>
       </x:c>
       <x:c r="B6" s="26" t="str">
-        <x:v>После первого запуска фильтры появятся в строке заголовков. Можно выбрать IP, локацию, статус или дату.</x:v>
+        <x:v>После первого запуска фильтры появятся в строке заголовков. Можно выбрать IP, статус или дату.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -532,10 +464,10 @@
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="16" t="str">
-        <x:v>Остаток, %</x:v>
+        <x:v>Счётчики</x:v>
       </x:c>
       <x:c r="B8" s="26" t="str">
-        <x:v>Хранится как числовой процент, поэтому его можно сортировать и использовать в формулах.</x:v>
+        <x:v>Значения печати и сканирования хранятся как числа, поэтому их можно сортировать и использовать в формулах.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -548,7 +480,7 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:H2"/>
+    <x:mergeCell ref="A1:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
